--- a/Salary_Calculation.xlsx
+++ b/Salary_Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{506228A4-4AD3-46EB-8C0D-42A49F4DBA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87688BC7-CFE8-4971-9878-FBE862E1B149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{7C07EA9C-7350-4ED6-A10A-AE57C94EE8E9}"/>
   </bookViews>
@@ -228,9 +228,6 @@
     <t>TA</t>
   </si>
   <si>
-    <t>Bonus</t>
-  </si>
-  <si>
     <t>Incentive</t>
   </si>
   <si>
@@ -276,6 +273,9 @@
   </si>
   <si>
     <t>*=if(f2,$b$4,4000,0)</t>
+  </si>
+  <si>
+    <t>Bonus for R&amp;D dept in south region</t>
   </si>
 </sst>
 </file>
@@ -658,7 +658,7 @@
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="27.08984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.90625" customWidth="1"/>
-    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.90625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.54296875" bestFit="1" customWidth="1"/>
@@ -666,7 +666,7 @@
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -698,22 +698,22 @@
         <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
@@ -1406,17 +1406,17 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Salary_Calculation.xlsx
+++ b/Salary_Calculation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87688BC7-CFE8-4971-9878-FBE862E1B149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16AD98C-679A-4C52-8AD7-D03CFE5F921A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{7C07EA9C-7350-4ED6-A10A-AE57C94EE8E9}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{7C07EA9C-7350-4ED6-A10A-AE57C94EE8E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>Emp Code</t>
   </si>
@@ -275,7 +275,13 @@
     <t>*=if(f2,$b$4,4000,0)</t>
   </si>
   <si>
-    <t>Bonus for R&amp;D dept in south region</t>
+    <t>Bonus for R&amp;D dept with south region</t>
+  </si>
+  <si>
+    <t>*=if(and(f2=$f$4,e2=$e$5),3000,0)</t>
+  </si>
+  <si>
+    <t>from dept training or region east</t>
   </si>
 </sst>
 </file>
@@ -285,7 +291,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0.00;[Red]&quot;₹&quot;#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="&quot;₹&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="&quot;₹&quot;#,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -330,7 +336,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -645,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8598D7C-B927-4C49-B642-925C296961BE}">
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
@@ -658,7 +664,7 @@
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="27.08984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.90625" customWidth="1"/>
-    <col min="11" max="11" width="31" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.90625" customWidth="1"/>
     <col min="12" max="12" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.90625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.54296875" bestFit="1" customWidth="1"/>
@@ -666,7 +672,7 @@
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -716,7 +722,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -750,8 +756,24 @@
         <f>IF(F2=$F$4,4000,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K2">
+        <f>IF(AND(F2=$F$5,E2=$E$5),3000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>IF(OR(F2=$F$2,E2=$E$7),5000,10)</f>
+        <v>5000</v>
+      </c>
+      <c r="M2" s="4">
+        <f>G2*15%</f>
+        <v>1500</v>
+      </c>
+      <c r="R2">
+        <f>IF(F2=$F$5,50000,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -785,8 +807,24 @@
         <f t="shared" ref="J3:J21" si="2">IF(F3=$F$4,4000,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K3">
+        <f t="shared" ref="K3:K21" si="3">IF(AND(F3=$F$5,E3=$E$5),3000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L21" si="4">IF(OR(F3=$F$2,E3=$E$7),5000,10)</f>
+        <v>10</v>
+      </c>
+      <c r="M3" s="4">
+        <f t="shared" ref="M3:M21" si="5">G3*15%</f>
+        <v>1800</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q21" si="6">IF(F3=$F$5,50000,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -817,8 +855,24 @@
         <f>IF(F4=$F$4,4000,0)</f>
         <v>4000</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="M4" s="4">
+        <f t="shared" si="5"/>
+        <v>1687.5</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -852,8 +906,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K5">
+        <f t="shared" si="3"/>
+        <v>3000</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="M5" s="4">
+        <f t="shared" si="5"/>
+        <v>1800</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="6"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -884,8 +954,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+      <c r="M6" s="4">
+        <f t="shared" si="5"/>
+        <v>2437.5</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -919,8 +1005,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+      <c r="M7" s="4">
+        <f t="shared" si="5"/>
+        <v>960</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -954,8 +1056,24 @@
         <f>IF(F8=$F$4,4000,0)</f>
         <v>4000</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+      <c r="M8" s="4">
+        <f t="shared" si="5"/>
+        <v>675</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -989,8 +1107,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+      <c r="M9" s="4">
+        <f t="shared" si="5"/>
+        <v>941.25</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="6"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1024,8 +1158,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+      <c r="M10" s="4">
+        <f t="shared" si="5"/>
+        <v>937.5</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1056,8 +1206,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="M11" s="4">
+        <f t="shared" si="5"/>
+        <v>1312.5</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1091,8 +1257,24 @@
         <f>IF(F12=$F$4,4000,0)</f>
         <v>4000</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="M12" s="4">
+        <f t="shared" si="5"/>
+        <v>1687.5</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1126,8 +1308,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K13">
+        <f t="shared" si="3"/>
+        <v>3000</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="M13" s="4">
+        <f t="shared" si="5"/>
+        <v>1500</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1161,8 +1359,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+      <c r="M14" s="4">
+        <f t="shared" si="5"/>
+        <v>2437.5</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1196,8 +1410,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="M15" s="4">
+        <f t="shared" si="5"/>
+        <v>960</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1231,8 +1461,24 @@
         <f>IF(F16=$F$4,4000,0)</f>
         <v>4000</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="M16" s="4">
+        <f t="shared" si="5"/>
+        <v>675</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1263,8 +1509,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K17">
+        <f t="shared" si="3"/>
+        <v>3000</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="M17" s="4">
+        <f t="shared" si="5"/>
+        <v>941.25</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="6"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1298,8 +1560,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="M18" s="4">
+        <f t="shared" si="5"/>
+        <v>937.5</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1333,8 +1611,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="M19" s="4">
+        <f t="shared" si="5"/>
+        <v>1312.5</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="6"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1368,8 +1662,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="M20" s="4">
+        <f t="shared" si="5"/>
+        <v>1687.5</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1403,20 +1713,48 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+      <c r="M21" s="4">
+        <f t="shared" si="5"/>
+        <v>1500</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="J23" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K23" t="s">
+        <v>73</v>
+      </c>
+      <c r="L23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="J24" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="J25" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="I29">
+        <f>IF(F2=$F$5,50000,0)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Salary_Calculation.xlsx
+++ b/Salary_Calculation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16AD98C-679A-4C52-8AD7-D03CFE5F921A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634EF2D5-01DC-4D49-8FB3-DB009D2F2D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{7C07EA9C-7350-4ED6-A10A-AE57C94EE8E9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{7C07EA9C-7350-4ED6-A10A-AE57C94EE8E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="85">
   <si>
     <t>Emp Code</t>
   </si>
@@ -282,6 +282,36 @@
   </si>
   <si>
     <t>from dept training or region east</t>
+  </si>
+  <si>
+    <t>upto 5000</t>
+  </si>
+  <si>
+    <t>no tax</t>
+  </si>
+  <si>
+    <t>salary</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>5000 to 10000</t>
+  </si>
+  <si>
+    <t>10000 to 15000</t>
+  </si>
+  <si>
+    <t>15000 to 20000</t>
+  </si>
+  <si>
+    <t>&gt;20000</t>
+  </si>
+  <si>
+    <t>*=IF(G2&lt;5000,0,IF(G2&lt;10000,100,IF(G2&lt;15000,200,IF(G2&lt;20000,300,400))))</t>
+  </si>
+  <si>
+    <t>*=basic*15%</t>
   </si>
 </sst>
 </file>
@@ -651,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8598D7C-B927-4C49-B642-925C296961BE}">
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
@@ -661,18 +691,22 @@
     <col min="5" max="5" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="8" max="8" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.90625" customWidth="1"/>
-    <col min="11" max="11" width="32.90625" customWidth="1"/>
-    <col min="12" max="12" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="63.6328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -722,7 +756,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -768,12 +802,16 @@
         <f>G2*15%</f>
         <v>1500</v>
       </c>
+      <c r="N2">
+        <f>IF(G2&lt;5000,0,IF(G2&lt;10000,100,IF(G2&lt;15000,200,IF(G2&lt;20000,300,400))))</f>
+        <v>200</v>
+      </c>
       <c r="R2">
         <f>IF(F2=$F$5,50000,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -819,12 +857,16 @@
         <f t="shared" ref="M3:M21" si="5">G3*15%</f>
         <v>1800</v>
       </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N21" si="6">IF(G3&lt;5000,0,IF(G3&lt;10000,100,IF(G3&lt;15000,200,IF(G3&lt;20000,300,400))))</f>
+        <v>200</v>
+      </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q21" si="6">IF(F3=$F$5,50000,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+        <f t="shared" ref="Q3:Q21" si="7">IF(F3=$F$5,50000,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -867,12 +909,16 @@
         <f t="shared" si="5"/>
         <v>1687.5</v>
       </c>
+      <c r="N4">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
       <c r="Q4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -918,12 +964,16 @@
         <f t="shared" si="5"/>
         <v>1800</v>
       </c>
+      <c r="N5">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
       <c r="Q5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50000</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -966,12 +1016,16 @@
         <f t="shared" si="5"/>
         <v>2437.5</v>
       </c>
+      <c r="N6">
+        <f t="shared" si="6"/>
+        <v>300</v>
+      </c>
       <c r="Q6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1017,12 +1071,22 @@
         <f t="shared" si="5"/>
         <v>960</v>
       </c>
+      <c r="N7">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
       <c r="Q7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S7" t="s">
+        <v>77</v>
+      </c>
+      <c r="T7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1068,12 +1132,22 @@
         <f t="shared" si="5"/>
         <v>675</v>
       </c>
+      <c r="N8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="Q8">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S8" t="s">
+        <v>75</v>
+      </c>
+      <c r="T8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1119,12 +1193,22 @@
         <f t="shared" si="5"/>
         <v>941.25</v>
       </c>
+      <c r="N9">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
       <c r="Q9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50000</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S9" t="s">
+        <v>79</v>
+      </c>
+      <c r="T9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1170,12 +1254,22 @@
         <f t="shared" si="5"/>
         <v>937.5</v>
       </c>
+      <c r="N10">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
       <c r="Q10">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S10" t="s">
+        <v>80</v>
+      </c>
+      <c r="T10">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1218,12 +1312,22 @@
         <f t="shared" si="5"/>
         <v>1312.5</v>
       </c>
+      <c r="N11">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
       <c r="Q11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S11" t="s">
+        <v>81</v>
+      </c>
+      <c r="T11">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1269,12 +1373,22 @@
         <f t="shared" si="5"/>
         <v>1687.5</v>
       </c>
+      <c r="N12">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
       <c r="Q12">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S12" t="s">
+        <v>82</v>
+      </c>
+      <c r="T12">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1320,12 +1434,16 @@
         <f t="shared" si="5"/>
         <v>1500</v>
       </c>
+      <c r="N13">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
       <c r="Q13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50000</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1371,12 +1489,16 @@
         <f t="shared" si="5"/>
         <v>2437.5</v>
       </c>
+      <c r="N14">
+        <f t="shared" si="6"/>
+        <v>300</v>
+      </c>
       <c r="Q14">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1422,12 +1544,16 @@
         <f t="shared" si="5"/>
         <v>960</v>
       </c>
+      <c r="N15">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
       <c r="Q15">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1473,8 +1599,12 @@
         <f t="shared" si="5"/>
         <v>675</v>
       </c>
+      <c r="N16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="Q16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1521,8 +1651,12 @@
         <f t="shared" si="5"/>
         <v>941.25</v>
       </c>
+      <c r="N17">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
       <c r="Q17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50000</v>
       </c>
     </row>
@@ -1572,8 +1706,12 @@
         <f t="shared" si="5"/>
         <v>937.5</v>
       </c>
+      <c r="N18">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
       <c r="Q18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1623,8 +1761,12 @@
         <f t="shared" si="5"/>
         <v>1312.5</v>
       </c>
+      <c r="N19">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
       <c r="Q19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50000</v>
       </c>
     </row>
@@ -1674,8 +1816,12 @@
         <f t="shared" si="5"/>
         <v>1687.5</v>
       </c>
+      <c r="N20">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
       <c r="Q20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1725,8 +1871,12 @@
         <f t="shared" si="5"/>
         <v>1500</v>
       </c>
+      <c r="N21">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
       <c r="Q21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1739,6 +1889,12 @@
       </c>
       <c r="L23" t="s">
         <v>74</v>
+      </c>
+      <c r="M23" t="s">
+        <v>84</v>
+      </c>
+      <c r="N23" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">

--- a/Salary_Calculation.xlsx
+++ b/Salary_Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634EF2D5-01DC-4D49-8FB3-DB009D2F2D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C032B89-C520-4C35-AA97-A2288450A2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{7C07EA9C-7350-4ED6-A10A-AE57C94EE8E9}"/>
   </bookViews>
@@ -308,10 +308,10 @@
     <t>&gt;20000</t>
   </si>
   <si>
-    <t>*=IF(G2&lt;5000,0,IF(G2&lt;10000,100,IF(G2&lt;15000,200,IF(G2&lt;20000,300,400))))</t>
-  </si>
-  <si>
     <t>*=basic*15%</t>
+  </si>
+  <si>
+    <t>*=IF(G2&lt;=5000,0,IF(G2&lt;=10000,100,IF(G2&lt;=15000,200,IF(G2&lt;=20000,300,400))))</t>
   </si>
 </sst>
 </file>
@@ -681,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8598D7C-B927-4C49-B642-925C296961BE}">
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
@@ -697,8 +697,8 @@
     <col min="11" max="11" width="33.1796875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="28.26953125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="63.6328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="67.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="1.81640625" bestFit="1" customWidth="1"/>
@@ -706,7 +706,7 @@
     <col min="20" max="20" width="8.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -756,7 +756,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -803,15 +803,27 @@
         <v>1500</v>
       </c>
       <c r="N2">
-        <f>IF(G2&lt;5000,0,IF(G2&lt;10000,100,IF(G2&lt;15000,200,IF(G2&lt;20000,300,400))))</f>
-        <v>200</v>
+        <f>IF(G2&lt;=5000,0,IF(G2&lt;=10000,100,IF(G2&lt;=15000,200,IF(G2&lt;=20000,300,400))))</f>
+        <v>100</v>
+      </c>
+      <c r="O2" s="3">
+        <f>SUM(G2:L2)</f>
+        <v>17096</v>
+      </c>
+      <c r="P2" s="4">
+        <f>SUM(M2:O2)</f>
+        <v>18696</v>
       </c>
       <c r="R2">
         <f>IF(F2=$F$5,50000,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U2">
+        <f>IF(G2&lt;=5000,0,IF(G2&lt;=10000,100,IF(G2&lt;=15000,200,IF(G2&lt;=20000,300,400))))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -858,15 +870,27 @@
         <v>1800</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N21" si="6">IF(G3&lt;5000,0,IF(G3&lt;10000,100,IF(G3&lt;15000,200,IF(G3&lt;20000,300,400))))</f>
+        <f t="shared" ref="N3:N21" si="6">IF(G3&lt;=5000,0,IF(G3&lt;=10000,100,IF(G3&lt;=15000,200,IF(G3&lt;=20000,300,400))))</f>
         <v>200</v>
       </c>
+      <c r="O3" s="3">
+        <f t="shared" ref="O3:O21" si="7">SUM(G3:L3)</f>
+        <v>14525.2</v>
+      </c>
+      <c r="P3" s="4">
+        <f t="shared" ref="P3:P21" si="8">SUM(M3:O3)</f>
+        <v>16525.2</v>
+      </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q21" si="7">IF(F3=$F$5,50000,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" ref="Q3:Q21" si="9">IF(F3=$F$5,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U21" si="10">IF(G3&lt;=5000,0,IF(G3&lt;=10000,100,IF(G3&lt;=15000,200,IF(G3&lt;=20000,300,400))))</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -913,12 +937,24 @@
         <f t="shared" si="6"/>
         <v>200</v>
       </c>
+      <c r="O4" s="3">
+        <f t="shared" si="7"/>
+        <v>17618</v>
+      </c>
+      <c r="P4" s="4">
+        <f t="shared" si="8"/>
+        <v>19505.5</v>
+      </c>
       <c r="Q4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -968,12 +1004,24 @@
         <f t="shared" si="6"/>
         <v>200</v>
       </c>
+      <c r="O5" s="3">
+        <f t="shared" si="7"/>
+        <v>17525.2</v>
+      </c>
+      <c r="P5" s="4">
+        <f t="shared" si="8"/>
+        <v>19525.2</v>
+      </c>
       <c r="Q5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>50000</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U5">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1020,12 +1068,24 @@
         <f t="shared" si="6"/>
         <v>300</v>
       </c>
+      <c r="O6" s="3">
+        <f t="shared" si="7"/>
+        <v>24656</v>
+      </c>
+      <c r="P6" s="4">
+        <f t="shared" si="8"/>
+        <v>27393.5</v>
+      </c>
       <c r="Q6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="10"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1075,8 +1135,16 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
+      <c r="O7" s="3">
+        <f t="shared" si="7"/>
+        <v>12741.439999999999</v>
+      </c>
+      <c r="P7" s="4">
+        <f t="shared" si="8"/>
+        <v>13801.439999999999</v>
+      </c>
       <c r="Q7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S7" t="s">
@@ -1085,8 +1153,12 @@
       <c r="T7" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U7">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1136,8 +1208,16 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="O8" s="3">
+        <f t="shared" si="7"/>
+        <v>14443.2</v>
+      </c>
+      <c r="P8" s="4">
+        <f t="shared" si="8"/>
+        <v>15118.2</v>
+      </c>
       <c r="Q8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S8" t="s">
@@ -1146,8 +1226,12 @@
       <c r="T8" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1197,8 +1281,16 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
+      <c r="O9" s="3">
+        <f t="shared" si="7"/>
+        <v>12590.24</v>
+      </c>
+      <c r="P9" s="4">
+        <f t="shared" si="8"/>
+        <v>13631.49</v>
+      </c>
       <c r="Q9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>50000</v>
       </c>
       <c r="S9" t="s">
@@ -1207,8 +1299,12 @@
       <c r="T9">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U9">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1258,8 +1354,16 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
+      <c r="O10" s="3">
+        <f t="shared" si="7"/>
+        <v>12560</v>
+      </c>
+      <c r="P10" s="4">
+        <f t="shared" si="8"/>
+        <v>13597.5</v>
+      </c>
       <c r="Q10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S10" t="s">
@@ -1268,8 +1372,12 @@
       <c r="T10">
         <v>200</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U10">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1316,8 +1424,16 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
+      <c r="O11" s="3">
+        <f t="shared" si="7"/>
+        <v>10594</v>
+      </c>
+      <c r="P11" s="4">
+        <f t="shared" si="8"/>
+        <v>12006.5</v>
+      </c>
       <c r="Q11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S11" t="s">
@@ -1326,8 +1442,12 @@
       <c r="T11">
         <v>300</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U11">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1377,8 +1497,16 @@
         <f t="shared" si="6"/>
         <v>200</v>
       </c>
+      <c r="O12" s="3">
+        <f t="shared" si="7"/>
+        <v>17618</v>
+      </c>
+      <c r="P12" s="4">
+        <f t="shared" si="8"/>
+        <v>19505.5</v>
+      </c>
       <c r="Q12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S12" t="s">
@@ -1387,8 +1515,12 @@
       <c r="T12">
         <v>400</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U12">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1436,14 +1568,26 @@
       </c>
       <c r="N13">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>100</v>
+      </c>
+      <c r="O13" s="3">
+        <f t="shared" si="7"/>
+        <v>15106</v>
+      </c>
+      <c r="P13" s="4">
+        <f t="shared" si="8"/>
+        <v>16706</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>50000</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U13">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1493,12 +1637,24 @@
         <f t="shared" si="6"/>
         <v>300</v>
       </c>
+      <c r="O14" s="3">
+        <f t="shared" si="7"/>
+        <v>24656</v>
+      </c>
+      <c r="P14" s="4">
+        <f t="shared" si="8"/>
+        <v>27393.5</v>
+      </c>
       <c r="Q14">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="10"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1548,12 +1704,24 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
+      <c r="O15" s="3">
+        <f t="shared" si="7"/>
+        <v>7751.44</v>
+      </c>
+      <c r="P15" s="4">
+        <f t="shared" si="8"/>
+        <v>8811.4399999999987</v>
+      </c>
       <c r="Q15">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1603,12 +1771,24 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="O16" s="3">
+        <f t="shared" si="7"/>
+        <v>9453.2000000000007</v>
+      </c>
+      <c r="P16" s="4">
+        <f t="shared" si="8"/>
+        <v>10128.200000000001</v>
+      </c>
       <c r="Q16">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1655,12 +1835,24 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
+      <c r="O17" s="3">
+        <f t="shared" si="7"/>
+        <v>10600.24</v>
+      </c>
+      <c r="P17" s="4">
+        <f t="shared" si="8"/>
+        <v>11641.49</v>
+      </c>
       <c r="Q17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>50000</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="U17">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1710,12 +1902,24 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
+      <c r="O18" s="3">
+        <f t="shared" si="7"/>
+        <v>7570</v>
+      </c>
+      <c r="P18" s="4">
+        <f t="shared" si="8"/>
+        <v>8607.5</v>
+      </c>
       <c r="Q18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1765,12 +1969,24 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
+      <c r="O19" s="3">
+        <f t="shared" si="7"/>
+        <v>10594</v>
+      </c>
+      <c r="P19" s="4">
+        <f t="shared" si="8"/>
+        <v>12006.5</v>
+      </c>
       <c r="Q19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>50000</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="U19">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1820,12 +2036,24 @@
         <f t="shared" si="6"/>
         <v>200</v>
       </c>
+      <c r="O20" s="3">
+        <f t="shared" si="7"/>
+        <v>13618</v>
+      </c>
+      <c r="P20" s="4">
+        <f t="shared" si="8"/>
+        <v>15505.5</v>
+      </c>
       <c r="Q20">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1873,14 +2101,26 @@
       </c>
       <c r="N21">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>100</v>
+      </c>
+      <c r="O21" s="3">
+        <f t="shared" si="7"/>
+        <v>17096</v>
+      </c>
+      <c r="P21" s="4">
+        <f t="shared" si="8"/>
+        <v>18696</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="J23" t="s">
         <v>69</v>
       </c>
@@ -1891,30 +2131,30 @@
         <v>74</v>
       </c>
       <c r="M23" t="s">
+        <v>83</v>
+      </c>
+      <c r="N23" t="s">
         <v>84</v>
       </c>
-      <c r="N23" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="J24" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="J25" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="I29">
         <f>IF(F2=$F$5,50000,0)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B21" xr:uid="{FE087569-59FC-441A-BA17-DDC80A4A72B2}">
       <formula1>ISTEXT(B1)</formula1>
     </dataValidation>
